--- a/URL Regional Classification.xlsx
+++ b/URL Regional Classification.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="1" documentId="8_{F89B0BC0-E015-40C5-9255-28FA0E74F595}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{880ABFB8-D2E5-4C51-954E-D540B73FE8F9}"/>
   <bookViews>
-    <workbookView xWindow="-27420" yWindow="-720" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30195" yWindow="1395" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="12" r:id="rId1"/>
@@ -6373,13 +6373,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -6399,6 +6399,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -37743,7 +37747,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="22" t="s">
         <v>1261</v>
       </c>
       <c r="B1" s="20"/>
@@ -49749,7 +49753,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="20"/>
@@ -50068,7 +50072,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="21" t="s">
         <v>19</v>
       </c>
       <c r="B1" s="20"/>
@@ -51504,7 +51508,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="22" t="s">
         <v>95</v>
       </c>
       <c r="B1" s="20"/>
@@ -58300,7 +58304,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="23" t="s">
         <v>497</v>
       </c>
       <c r="B1" s="20"/>
@@ -59253,7 +59257,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="24" t="s">
         <v>574</v>
       </c>
       <c r="B1" s="20"/>
@@ -60413,7 +60417,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="25" t="s">
         <v>663</v>
       </c>
       <c r="B1" s="20"/>
